--- a/output/yearly_total_coral_cover_iteration_63_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_63_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.273254550349897</v>
+        <v>1.285595118992279</v>
       </c>
       <c r="C3" t="n">
-        <v>4.604766742862203</v>
+        <v>4.641061955488207</v>
       </c>
       <c r="D3" t="n">
-        <v>6.102352382730484</v>
+        <v>6.143016372640389</v>
       </c>
       <c r="E3" t="n">
-        <v>11.98037367594258</v>
+        <v>12.06967344712088</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.430171832502412</v>
+        <v>1.459334073950696</v>
       </c>
       <c r="C4" t="n">
-        <v>5.104122189994905</v>
+        <v>5.168739262019363</v>
       </c>
       <c r="D4" t="n">
-        <v>6.459306348492717</v>
+        <v>6.432335939019184</v>
       </c>
       <c r="E4" t="n">
-        <v>12.99360037099003</v>
+        <v>13.06040927498924</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.638709162486861</v>
+        <v>1.687373684921189</v>
       </c>
       <c r="C5" t="n">
-        <v>5.72984271006591</v>
+        <v>5.881619520578015</v>
       </c>
       <c r="D5" t="n">
-        <v>6.929181589349107</v>
+        <v>6.77208578894072</v>
       </c>
       <c r="E5" t="n">
-        <v>14.29773346190188</v>
+        <v>14.34107899443992</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.87625549464447</v>
+        <v>1.943866808131776</v>
       </c>
       <c r="C6" t="n">
-        <v>6.485381878196538</v>
+        <v>6.749948886984788</v>
       </c>
       <c r="D6" t="n">
-        <v>7.316938188477166</v>
+        <v>7.146368929615282</v>
       </c>
       <c r="E6" t="n">
-        <v>15.67857556131817</v>
+        <v>15.84018462473185</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.136598750709471</v>
+        <v>2.221365292166339</v>
       </c>
       <c r="C7" t="n">
-        <v>7.332871423386676</v>
+        <v>7.742382286885205</v>
       </c>
       <c r="D7" t="n">
-        <v>7.707518495471266</v>
+        <v>7.538230008734026</v>
       </c>
       <c r="E7" t="n">
-        <v>17.17698866956741</v>
+        <v>17.50197758778557</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.327575107519004</v>
+        <v>1.393966213852911</v>
       </c>
       <c r="C8" t="n">
-        <v>4.891209959660863</v>
+        <v>5.338585027806157</v>
       </c>
       <c r="D8" t="n">
-        <v>6.054172345503446</v>
+        <v>5.787849611772593</v>
       </c>
       <c r="E8" t="n">
-        <v>12.27295741268331</v>
+        <v>12.52040085343166</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.66504750541701</v>
+        <v>1.749832759456619</v>
       </c>
       <c r="C9" t="n">
-        <v>5.849327781462072</v>
+        <v>6.489889348830978</v>
       </c>
       <c r="D9" t="n">
-        <v>6.687726815452341</v>
+        <v>6.319170051526688</v>
       </c>
       <c r="E9" t="n">
-        <v>14.20210210233142</v>
+        <v>14.55889215981428</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.033176016687811</v>
+        <v>2.116211230521429</v>
       </c>
       <c r="C10" t="n">
-        <v>6.954175476196961</v>
+        <v>7.737209531781553</v>
       </c>
       <c r="D10" t="n">
-        <v>7.325346401774153</v>
+        <v>6.835457097791256</v>
       </c>
       <c r="E10" t="n">
-        <v>16.31269789465892</v>
+        <v>16.68887786009424</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.412114443558132</v>
+        <v>2.49107235340667</v>
       </c>
       <c r="C11" t="n">
-        <v>8.221443673621556</v>
+        <v>9.121873198578943</v>
       </c>
       <c r="D11" t="n">
-        <v>7.894763037740784</v>
+        <v>7.340758750230276</v>
       </c>
       <c r="E11" t="n">
-        <v>18.52832115492047</v>
+        <v>18.95370430221589</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.799371480679544</v>
+        <v>2.883791957244486</v>
       </c>
       <c r="C12" t="n">
-        <v>9.591554738512373</v>
+        <v>10.52937246716766</v>
       </c>
       <c r="D12" t="n">
-        <v>8.556501561983552</v>
+        <v>7.816388956225104</v>
       </c>
       <c r="E12" t="n">
-        <v>20.94742778117547</v>
+        <v>21.22955338063725</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.173432720564469</v>
+        <v>3.268982491229013</v>
       </c>
       <c r="C13" t="n">
-        <v>11.00033145347707</v>
+        <v>12.01865679990183</v>
       </c>
       <c r="D13" t="n">
-        <v>9.087388122146841</v>
+        <v>8.280013778391099</v>
       </c>
       <c r="E13" t="n">
-        <v>23.26115229618838</v>
+        <v>23.56765306952195</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.834071608642764</v>
+        <v>1.898523345426567</v>
       </c>
       <c r="C14" t="n">
-        <v>7.848091147749003</v>
+        <v>8.516376627506848</v>
       </c>
       <c r="D14" t="n">
-        <v>6.871517253903572</v>
+        <v>6.253379446878652</v>
       </c>
       <c r="E14" t="n">
-        <v>16.55368001029534</v>
+        <v>16.66827941981207</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.890227577325681</v>
+        <v>1.963249971567559</v>
       </c>
       <c r="C15" t="n">
-        <v>8.426536895091223</v>
+        <v>9.10930315348671</v>
       </c>
       <c r="D15" t="n">
-        <v>6.951431517029262</v>
+        <v>6.249648805602516</v>
       </c>
       <c r="E15" t="n">
-        <v>17.26819598944617</v>
+        <v>17.32220193065679</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.205830011809903</v>
+        <v>2.302757962650191</v>
       </c>
       <c r="C16" t="n">
-        <v>9.90318361704885</v>
+        <v>10.70780440049545</v>
       </c>
       <c r="D16" t="n">
-        <v>7.534354033902849</v>
+        <v>6.6498288048076</v>
       </c>
       <c r="E16" t="n">
-        <v>19.6433676627616</v>
+        <v>19.66039116795324</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.779712238258618</v>
+        <v>1.864819946739774</v>
       </c>
       <c r="C17" t="n">
-        <v>9.099466041490157</v>
+        <v>9.820392833149716</v>
       </c>
       <c r="D17" t="n">
-        <v>7.049753549609582</v>
+        <v>6.138956751948688</v>
       </c>
       <c r="E17" t="n">
-        <v>17.92893182935835</v>
+        <v>17.82416953183818</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.038334035988355</v>
+        <v>2.153542129081718</v>
       </c>
       <c r="C18" t="n">
-        <v>10.56734575644886</v>
+        <v>11.42154479895992</v>
       </c>
       <c r="D18" t="n">
-        <v>7.558554114812534</v>
+        <v>6.524528345314581</v>
       </c>
       <c r="E18" t="n">
-        <v>20.16423390724975</v>
+        <v>20.09961527335622</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.054532873108427</v>
+        <v>2.184899150755362</v>
       </c>
       <c r="C19" t="n">
-        <v>11.25830960817481</v>
+        <v>12.17119752844575</v>
       </c>
       <c r="D19" t="n">
-        <v>7.737703435883491</v>
+        <v>6.605139649310286</v>
       </c>
       <c r="E19" t="n">
-        <v>21.05054591716673</v>
+        <v>20.9612363285114</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.290260314375129</v>
+        <v>2.451620367045135</v>
       </c>
       <c r="C20" t="n">
-        <v>12.88411325883865</v>
+        <v>13.91717691558645</v>
       </c>
       <c r="D20" t="n">
-        <v>8.247780273101965</v>
+        <v>6.98471276420323</v>
       </c>
       <c r="E20" t="n">
-        <v>23.42215384631575</v>
+        <v>23.35351004683481</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.364138435050943</v>
+        <v>1.46965667830339</v>
       </c>
       <c r="C21" t="n">
-        <v>9.457087277716143</v>
+        <v>10.18646691710927</v>
       </c>
       <c r="D21" t="n">
-        <v>6.918307349487976</v>
+        <v>5.79827066362096</v>
       </c>
       <c r="E21" t="n">
-        <v>17.73953306225506</v>
+        <v>17.45439425903362</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_63_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_63_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.285595118992279</v>
+        <v>1.286419787063847</v>
       </c>
       <c r="C3" t="n">
-        <v>4.641061955488207</v>
+        <v>4.586908752121954</v>
       </c>
       <c r="D3" t="n">
-        <v>6.143016372640389</v>
+        <v>6.019208169657823</v>
       </c>
       <c r="E3" t="n">
-        <v>12.06967344712088</v>
+        <v>11.89253670884362</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.459334073950696</v>
+        <v>1.461524326200086</v>
       </c>
       <c r="C4" t="n">
-        <v>5.168739262019363</v>
+        <v>5.022618045245659</v>
       </c>
       <c r="D4" t="n">
-        <v>6.432335939019184</v>
+        <v>6.38360556030979</v>
       </c>
       <c r="E4" t="n">
-        <v>13.06040927498924</v>
+        <v>12.86774793175553</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.687373684921189</v>
+        <v>1.699707079166006</v>
       </c>
       <c r="C5" t="n">
-        <v>5.881619520578015</v>
+        <v>5.547064982758358</v>
       </c>
       <c r="D5" t="n">
-        <v>6.77208578894072</v>
+        <v>6.725045645774859</v>
       </c>
       <c r="E5" t="n">
-        <v>14.34107899443992</v>
+        <v>13.97181770769922</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.943866808131776</v>
+        <v>1.971887815794803</v>
       </c>
       <c r="C6" t="n">
-        <v>6.749948886984788</v>
+        <v>6.170106093608293</v>
       </c>
       <c r="D6" t="n">
-        <v>7.146368929615282</v>
+        <v>7.043336385943585</v>
       </c>
       <c r="E6" t="n">
-        <v>15.84018462473185</v>
+        <v>15.18533029534668</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.221365292166339</v>
+        <v>2.29825291632556</v>
       </c>
       <c r="C7" t="n">
-        <v>7.742382286885205</v>
+        <v>6.936365619415296</v>
       </c>
       <c r="D7" t="n">
-        <v>7.538230008734026</v>
+        <v>7.385775849206365</v>
       </c>
       <c r="E7" t="n">
-        <v>17.50197758778557</v>
+        <v>16.62039438494722</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.393966213852911</v>
+        <v>1.531619382105845</v>
       </c>
       <c r="C8" t="n">
-        <v>5.338585027806157</v>
+        <v>4.678840438506492</v>
       </c>
       <c r="D8" t="n">
-        <v>5.787849611772593</v>
+        <v>5.604160507808598</v>
       </c>
       <c r="E8" t="n">
-        <v>12.52040085343166</v>
+        <v>11.81462032842093</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.749832759456619</v>
+        <v>2.002497108703514</v>
       </c>
       <c r="C9" t="n">
-        <v>6.489889348830978</v>
+        <v>5.801617793264565</v>
       </c>
       <c r="D9" t="n">
-        <v>6.319170051526688</v>
+        <v>6.0778819375669</v>
       </c>
       <c r="E9" t="n">
-        <v>14.55889215981428</v>
+        <v>13.88199683953498</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.116211230521429</v>
+        <v>2.492364060604484</v>
       </c>
       <c r="C10" t="n">
-        <v>7.737209531781553</v>
+        <v>7.122087232844504</v>
       </c>
       <c r="D10" t="n">
-        <v>6.835457097791256</v>
+        <v>6.651479304783841</v>
       </c>
       <c r="E10" t="n">
-        <v>16.68887786009424</v>
+        <v>16.26593059823283</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.49107235340667</v>
+        <v>2.990553038339962</v>
       </c>
       <c r="C11" t="n">
-        <v>9.121873198578943</v>
+        <v>8.558359411492447</v>
       </c>
       <c r="D11" t="n">
-        <v>7.340758750230276</v>
+        <v>7.220278315409078</v>
       </c>
       <c r="E11" t="n">
-        <v>18.95370430221589</v>
+        <v>18.76919076524149</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.883791957244486</v>
+        <v>3.483734985422321</v>
       </c>
       <c r="C12" t="n">
-        <v>10.52937246716766</v>
+        <v>10.0772898247445</v>
       </c>
       <c r="D12" t="n">
-        <v>7.816388956225104</v>
+        <v>7.682687911296383</v>
       </c>
       <c r="E12" t="n">
-        <v>21.22955338063725</v>
+        <v>21.24371272146321</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.268982491229013</v>
+        <v>3.965798484605952</v>
       </c>
       <c r="C13" t="n">
-        <v>12.01865679990183</v>
+        <v>11.66076581649101</v>
       </c>
       <c r="D13" t="n">
-        <v>8.280013778391099</v>
+        <v>8.091077486984632</v>
       </c>
       <c r="E13" t="n">
-        <v>23.56765306952195</v>
+        <v>23.71764178808159</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.898523345426567</v>
+        <v>2.262516124253114</v>
       </c>
       <c r="C14" t="n">
-        <v>8.516376627506848</v>
+        <v>8.119230228707886</v>
       </c>
       <c r="D14" t="n">
-        <v>6.253379446878652</v>
+        <v>6.14577008101616</v>
       </c>
       <c r="E14" t="n">
-        <v>16.66827941981207</v>
+        <v>16.52751643397716</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.963249971567559</v>
+        <v>2.362821287196011</v>
       </c>
       <c r="C15" t="n">
-        <v>9.10930315348671</v>
+        <v>8.890127978513609</v>
       </c>
       <c r="D15" t="n">
-        <v>6.249648805602516</v>
+        <v>6.157433243742613</v>
       </c>
       <c r="E15" t="n">
-        <v>17.32220193065679</v>
+        <v>17.41038250945223</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.302757962650191</v>
+        <v>2.785218236948201</v>
       </c>
       <c r="C16" t="n">
-        <v>10.70780440049545</v>
+        <v>10.63471328391428</v>
       </c>
       <c r="D16" t="n">
-        <v>6.6498288048076</v>
+        <v>6.605385086236347</v>
       </c>
       <c r="E16" t="n">
-        <v>19.66039116795324</v>
+        <v>20.02531660709882</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.864819946739774</v>
+        <v>2.258422236326405</v>
       </c>
       <c r="C17" t="n">
-        <v>9.820392833149716</v>
+        <v>9.982243759671846</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138956751948688</v>
+        <v>6.114403241865475</v>
       </c>
       <c r="E17" t="n">
-        <v>17.82416953183818</v>
+        <v>18.35506923786373</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.153542129081718</v>
+        <v>2.603290569874225</v>
       </c>
       <c r="C18" t="n">
-        <v>11.42154479895992</v>
+        <v>11.73836460059741</v>
       </c>
       <c r="D18" t="n">
-        <v>6.524528345314581</v>
+        <v>6.501290377155057</v>
       </c>
       <c r="E18" t="n">
-        <v>20.09961527335622</v>
+        <v>20.84294554762669</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.184899150755362</v>
+        <v>2.631407824123854</v>
       </c>
       <c r="C19" t="n">
-        <v>12.17119752844575</v>
+        <v>12.65018241587072</v>
       </c>
       <c r="D19" t="n">
-        <v>6.605139649310286</v>
+        <v>6.57528470162414</v>
       </c>
       <c r="E19" t="n">
-        <v>20.9612363285114</v>
+        <v>21.85687494161872</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.451620367045135</v>
+        <v>2.942867283296154</v>
       </c>
       <c r="C20" t="n">
-        <v>13.91717691558645</v>
+        <v>14.59123507184526</v>
       </c>
       <c r="D20" t="n">
-        <v>6.98471276420323</v>
+        <v>6.967355464792146</v>
       </c>
       <c r="E20" t="n">
-        <v>23.35351004683481</v>
+        <v>24.50145781993356</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.46965667830339</v>
+        <v>1.75231165983309</v>
       </c>
       <c r="C21" t="n">
-        <v>10.18646691710927</v>
+        <v>10.74127217973323</v>
       </c>
       <c r="D21" t="n">
-        <v>5.79827066362096</v>
+        <v>5.793842981474807</v>
       </c>
       <c r="E21" t="n">
-        <v>17.45439425903362</v>
+        <v>18.28742682104112</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_63_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_63_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.286419787063847</v>
+        <v>2.585353561201165</v>
       </c>
       <c r="C3" t="n">
-        <v>4.586908752121954</v>
+        <v>7.68632574787676</v>
       </c>
       <c r="D3" t="n">
-        <v>6.019208169657823</v>
+        <v>8.161011216058052</v>
       </c>
       <c r="E3" t="n">
-        <v>11.89253670884362</v>
+        <v>18.43269052513597</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.461524326200086</v>
+        <v>1.060726746981533</v>
       </c>
       <c r="C4" t="n">
-        <v>5.022618045245659</v>
+        <v>4.516665742837437</v>
       </c>
       <c r="D4" t="n">
-        <v>6.38360556030979</v>
+        <v>5.745158596648214</v>
       </c>
       <c r="E4" t="n">
-        <v>12.86774793175553</v>
+        <v>11.32255108646718</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.699707079166006</v>
+        <v>1.143242226409731</v>
       </c>
       <c r="C5" t="n">
-        <v>5.547064982758358</v>
+        <v>5.221496843826541</v>
       </c>
       <c r="D5" t="n">
-        <v>6.725045645774859</v>
+        <v>6.009016318283281</v>
       </c>
       <c r="E5" t="n">
-        <v>13.97181770769922</v>
+        <v>12.37375538851955</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.971887815794803</v>
+        <v>1.244057436695033</v>
       </c>
       <c r="C6" t="n">
-        <v>6.170106093608293</v>
+        <v>6.127599509579247</v>
       </c>
       <c r="D6" t="n">
-        <v>7.043336385943585</v>
+        <v>6.270831075792899</v>
       </c>
       <c r="E6" t="n">
-        <v>15.18533029534668</v>
+        <v>13.64248802206718</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.29825291632556</v>
+        <v>1.36130887094608</v>
       </c>
       <c r="C7" t="n">
-        <v>6.936365619415296</v>
+        <v>7.22486631477272</v>
       </c>
       <c r="D7" t="n">
-        <v>7.385775849206365</v>
+        <v>6.551726958534156</v>
       </c>
       <c r="E7" t="n">
-        <v>16.62039438494722</v>
+        <v>15.13790214425295</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.531619382105845</v>
+        <v>1.490227972620993</v>
       </c>
       <c r="C8" t="n">
-        <v>4.678840438506492</v>
+        <v>8.497627137584191</v>
       </c>
       <c r="D8" t="n">
-        <v>5.604160507808598</v>
+        <v>6.892208506748982</v>
       </c>
       <c r="E8" t="n">
-        <v>11.81462032842093</v>
+        <v>16.88006361695417</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.002497108703514</v>
+        <v>1.61237744321221</v>
       </c>
       <c r="C9" t="n">
-        <v>5.801617793264565</v>
+        <v>9.887745915251282</v>
       </c>
       <c r="D9" t="n">
-        <v>6.0778819375669</v>
+        <v>7.27087185188442</v>
       </c>
       <c r="E9" t="n">
-        <v>13.88199683953498</v>
+        <v>18.77099521034791</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.492364060604484</v>
+        <v>1.013546512387365</v>
       </c>
       <c r="C10" t="n">
-        <v>7.122087232844504</v>
+        <v>7.217161168137747</v>
       </c>
       <c r="D10" t="n">
-        <v>6.651479304783841</v>
+        <v>5.714635576696173</v>
       </c>
       <c r="E10" t="n">
-        <v>16.26593059823283</v>
+        <v>13.94534325722129</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.990553038339962</v>
+        <v>0.9576261631534663</v>
       </c>
       <c r="C11" t="n">
-        <v>8.558359411492447</v>
+        <v>7.786083962748773</v>
       </c>
       <c r="D11" t="n">
-        <v>7.220278315409078</v>
+        <v>5.528339132338298</v>
       </c>
       <c r="E11" t="n">
-        <v>18.76919076524149</v>
+        <v>14.27204925824054</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.483734985422321</v>
+        <v>1.044137770851695</v>
       </c>
       <c r="C12" t="n">
-        <v>10.0772898247445</v>
+        <v>9.280343238520588</v>
       </c>
       <c r="D12" t="n">
-        <v>7.682687911296383</v>
+        <v>5.818406309035062</v>
       </c>
       <c r="E12" t="n">
-        <v>21.24371272146321</v>
+        <v>16.14288731840735</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.965798484605952</v>
+        <v>0.8367828382377266</v>
       </c>
       <c r="C13" t="n">
-        <v>11.66076581649101</v>
+        <v>8.889362215304297</v>
       </c>
       <c r="D13" t="n">
-        <v>8.091077486984632</v>
+        <v>5.25033763492673</v>
       </c>
       <c r="E13" t="n">
-        <v>23.71764178808159</v>
+        <v>14.97648268846875</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.262516124253114</v>
+        <v>0.9149103205416875</v>
       </c>
       <c r="C14" t="n">
-        <v>8.119230228707886</v>
+        <v>10.4784681367834</v>
       </c>
       <c r="D14" t="n">
-        <v>6.14577008101616</v>
+        <v>5.515507689843792</v>
       </c>
       <c r="E14" t="n">
-        <v>16.52751643397716</v>
+        <v>16.90888614716888</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.362821287196011</v>
+        <v>0.8945194207244813</v>
       </c>
       <c r="C15" t="n">
-        <v>8.890127978513609</v>
+        <v>11.36852060545355</v>
       </c>
       <c r="D15" t="n">
-        <v>6.157433243742613</v>
+        <v>5.50065384707854</v>
       </c>
       <c r="E15" t="n">
-        <v>17.41038250945223</v>
+        <v>17.76369387325657</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.785218236948201</v>
+        <v>0.9821011334203393</v>
       </c>
       <c r="C16" t="n">
-        <v>10.63471328391428</v>
+        <v>13.33552085325134</v>
       </c>
       <c r="D16" t="n">
-        <v>6.605385086236347</v>
+        <v>5.822873261089385</v>
       </c>
       <c r="E16" t="n">
-        <v>20.02531660709882</v>
+        <v>20.14049524776106</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.258422236326405</v>
+        <v>0.5894315041527425</v>
       </c>
       <c r="C17" t="n">
-        <v>9.982243759671846</v>
+        <v>10.01310990749337</v>
       </c>
       <c r="D17" t="n">
-        <v>6.114403241865475</v>
+        <v>4.793324261122796</v>
       </c>
       <c r="E17" t="n">
-        <v>18.35506923786373</v>
+        <v>15.3958656727689</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.603290569874225</v>
+        <v>0.4697171890968864</v>
       </c>
       <c r="C18" t="n">
-        <v>11.73836460059741</v>
+        <v>9.040089940337309</v>
       </c>
       <c r="D18" t="n">
-        <v>6.501290377155057</v>
+        <v>4.286575548621721</v>
       </c>
       <c r="E18" t="n">
-        <v>20.84294554762669</v>
+        <v>13.79638267805592</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.631407824123854</v>
+        <v>0.5513396932279663</v>
       </c>
       <c r="C19" t="n">
-        <v>12.65018241587072</v>
+        <v>11.2401374581692</v>
       </c>
       <c r="D19" t="n">
-        <v>6.57528470162414</v>
+        <v>4.684281543612104</v>
       </c>
       <c r="E19" t="n">
-        <v>21.85687494161872</v>
+        <v>16.47575869500927</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.942867283296154</v>
+        <v>0.6277982044347079</v>
       </c>
       <c r="C20" t="n">
-        <v>14.59123507184526</v>
+        <v>13.56017418041414</v>
       </c>
       <c r="D20" t="n">
-        <v>6.967355464792146</v>
+        <v>5.066093043270731</v>
       </c>
       <c r="E20" t="n">
-        <v>24.50145781993356</v>
+        <v>19.25406542811957</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.75231165983309</v>
+        <v>0.6972961244183397</v>
       </c>
       <c r="C21" t="n">
-        <v>10.74127217973323</v>
+        <v>15.96749809104365</v>
       </c>
       <c r="D21" t="n">
-        <v>5.793842981474807</v>
+        <v>5.470121493476463</v>
       </c>
       <c r="E21" t="n">
-        <v>18.28742682104112</v>
+        <v>22.13491570893846</v>
       </c>
     </row>
   </sheetData>
